--- a/Result/profitability/3006.xlsx
+++ b/Result/profitability/3006.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.12</v>
       </c>
       <c r="M2" t="n">
-        <v>1.16875</v>
+        <v>3.6025</v>
       </c>
       <c r="N2" t="n">
-        <v>18.95375</v>
+        <v>25.5125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.32</v>
       </c>
       <c r="M3" t="n">
-        <v>1.11625</v>
+        <v>3.59375</v>
       </c>
       <c r="N3" t="n">
-        <v>18.70625</v>
+        <v>25.99875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.06875</v>
+        <v>3.62875</v>
       </c>
       <c r="N4" t="n">
-        <v>17.8575</v>
+        <v>24.9675</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.24</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0725</v>
+        <v>3.9225</v>
       </c>
       <c r="N5" t="n">
-        <v>17.02125</v>
+        <v>25.1275</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.28</v>
       </c>
       <c r="M6" t="n">
-        <v>1.36125</v>
+        <v>3.88125</v>
       </c>
       <c r="N6" t="n">
-        <v>17.03</v>
+        <v>24.0025</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.14</v>
       </c>
       <c r="M7" t="n">
-        <v>1.3375</v>
+        <v>3.4025</v>
       </c>
       <c r="N7" t="n">
-        <v>16.8825</v>
+        <v>21.42875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.31</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9149999999999999</v>
+        <v>2.53875</v>
       </c>
       <c r="N8" t="n">
-        <v>15.04875</v>
+        <v>17.69625</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.72</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1025000000000001</v>
+        <v>0.1025</v>
       </c>
       <c r="N9" t="n">
         <v>12.24375</v>
@@ -1645,7 +1645,7 @@
         <v>1.16</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2325000000000001</v>
+        <v>0.2325</v>
       </c>
       <c r="N10" t="n">
         <v>12.65375</v>
@@ -1772,7 +1772,7 @@
         <v>1.49</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3787500000000001</v>
+        <v>0.37875</v>
       </c>
       <c r="N11" t="n">
         <v>13.9025</v>
@@ -1899,7 +1899,7 @@
         <v>0.45</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4337500000000001</v>
+        <v>0.43375</v>
       </c>
       <c r="N12" t="n">
         <v>16.6425</v>
@@ -2026,7 +2026,7 @@
         <v>-1.54</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2712500000000001</v>
+        <v>0.27125</v>
       </c>
       <c r="N13" t="n">
         <v>14.08125</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3006</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>13946</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4366</v>
+      </c>
+      <c r="E75" t="n">
+        <v>9581</v>
+      </c>
+      <c r="F75" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="G75" t="n">
+        <v>7173</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>51.43%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>160</v>
+      </c>
+      <c r="J75" t="n">
+        <v>7332</v>
+      </c>
+      <c r="K75" t="n">
+        <v>5908</v>
+      </c>
+      <c r="L75" t="n">
+        <v>20.21</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="N75" t="n">
+        <v>25.46625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.799168975069252</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.4457070707070707</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-8.803088803088805</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>64.85000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>16.84415584415584</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
